--- a/out/MLP-Mamba1_repeat_4_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_4_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.740833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.340833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6603920562098147</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.260392056209815</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.740833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.740833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.260392056209815</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.260392056209815</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.260392056209815</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6603920562098147</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.260392056209815</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002911884595637675</v>
+        <v>-0.0002493951768748229</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.125377296347919</v>
+        <v>0.1073822151692354</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.251089191551114</v>
+        <v>0.2150512200506935</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.484397974606741</v>
+        <v>0.4148751140107412</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.340833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.094830122634362</v>
+        <v>0.9376936231166811</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1490040413962465</v>
+        <v>0.1276174017282065</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.9078253670111168</v>
+        <v>0.7775291348393782</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.030234028388017</v>
+        <v>0.02589452011167235</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.740833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8190562797880638</v>
+        <v>0.7015005222852633</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02618365448335649</v>
+        <v>0.02242616303212245</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8411568527291149</v>
+        <v>0.7204292879116938</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01280094425877406</v>
+        <v>0.01096364213680528</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.740833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.840540595716174</v>
+        <v>0.7199014814297972</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006107433898408667</v>
+        <v>0.005230124573024914</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8399394289787253</v>
+        <v>0.719385881693471</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002541392468708027</v>
+        <v>0.002175633865310307</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.740833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.838907762413118</v>
+        <v>0.7185015718171071</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001759812697689741</v>
+        <v>0.001506704448961173</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8398836897104224</v>
+        <v>0.7193368151819601</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000731420068048378</v>
+        <v>0.0006257569961674208</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8395854436514759</v>
+        <v>0.7190806263736833</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003771941615533185</v>
+        <v>0.0003224040894425281</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8396069994625589</v>
+        <v>0.7190983752328278</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001451111287247665</v>
+        <v>0.000123591701180307</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8395195778236685</v>
+        <v>0.7190227692834286</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.68865563710321e-05</v>
+        <v>6.486125788297844e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8395280723895645</v>
+        <v>0.7190293299564242</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.509169298536786e-05</v>
+        <v>2.944497566348506e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8395218419288641</v>
+        <v>0.7190232716773584</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.41817221615223e-05</v>
+        <v>1.151759408353309e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.839514501695981</v>
+        <v>0.7190162564768202</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.301093358848441e-06</v>
+        <v>1.917577799040367e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8395068983321173</v>
+        <v>0.7190090152670836</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-1.69277857293039e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8395010276058132</v>
+        <v>0.7190032412881467</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.839495162809812</v>
+        <v>0.7189974721452792</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.260392056209815</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8394894836331038</v>
+        <v>0.7189919284771767</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8394846023348544</v>
+        <v>0.7189870073234553</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8394796811333066</v>
+        <v>0.7189870471789276</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8394796731622122</v>
+        <v>0.7189870392078331</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8394798325841012</v>
+        <v>0.7189871986297223</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.7189871029765887</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8394800876591241</v>
+        <v>0.718987453704745</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8394798405551956</v>
+        <v>0.7189872066008167</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8394798006997234</v>
+        <v>0.7189871667453445</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.740833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.7189871029765887</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8394798086708178</v>
+        <v>0.7189871747164389</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.7189871029765887</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.740833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8394798405551956</v>
+        <v>0.7189872066008167</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8394799362083294</v>
+        <v>0.7189873022539504</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8394798724395736</v>
+        <v>0.7189872384851945</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8394798325841012</v>
+        <v>0.7189871986297223</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8394798086708178</v>
+        <v>0.7189871747164389</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8394795615668897</v>
+        <v>0.7189869276125107</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.260392056209815</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.839479481855945</v>
+        <v>0.718986847901566</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8394795296825117</v>
+        <v>0.7189868957281327</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8394796492489288</v>
+        <v>0.7189870152945498</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6603920562098147</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8394796333067398</v>
+        <v>0.7189869993523609</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8394796492489288</v>
+        <v>0.7189870152945498</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8394796333067398</v>
+        <v>0.7189869993523609</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8394796891044011</v>
+        <v>0.718987055150022</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8394796891044011</v>
+        <v>0.718987055150022</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.340833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8394796891044011</v>
+        <v>0.718987055150022</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6603920562098147</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8394798405551956</v>
+        <v>0.7189872066008167</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8394800557747463</v>
+        <v>0.7189874218203672</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8394799680927072</v>
+        <v>0.7189873341383282</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8394799202661405</v>
+        <v>0.7189872863117615</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8394799680927072</v>
+        <v>0.7189873341383282</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8394797847575345</v>
+        <v>0.7189871508031555</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8394797927286289</v>
+        <v>0.7189871587742499</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.740833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8394798006997234</v>
+        <v>0.7189871667453445</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8394798086708178</v>
+        <v>0.7189871747164389</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6603920562098147</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8394798086708178</v>
+        <v>0.7189871747164389</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.740833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8394798485262902</v>
+        <v>0.7189872145719112</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.839479912295046</v>
+        <v>0.718987278340667</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8394800238903684</v>
+        <v>0.7189873899359894</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8394800717169352</v>
+        <v>0.7189874377625561</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8394800318614629</v>
+        <v>0.7189873979070839</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.740833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8394799601216127</v>
+        <v>0.7189873261672337</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8394800796880296</v>
+        <v>0.7189874457336506</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8394799202661405</v>
+        <v>0.7189872863117615</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8394796891044011</v>
+        <v>0.718987055150022</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.260392056209815</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8394796412778343</v>
+        <v>0.7189870073234553</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.260392056209815</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8394796731622122</v>
+        <v>0.7189870392078331</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.260392056209815</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.7189871029765887</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.7189871029765887</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8394796572200233</v>
+        <v>0.7189870232656442</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8394795376536062</v>
+        <v>0.7189869036992271</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.340833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8394794977981339</v>
+        <v>0.7189868638437549</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8394796412778343</v>
+        <v>0.7189870073234553</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6603920562098147</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.83947977678644</v>
+        <v>0.718987142832061</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8394797608442511</v>
+        <v>0.7189871268898721</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.7189871029765887</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8394796970754955</v>
+        <v>0.7189870631211165</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.260392056209815</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8394795934512675</v>
+        <v>0.7189869594968885</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.340833119445856</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8394794738848506</v>
+        <v>0.7189868399304715</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8394795934512675</v>
+        <v>0.7189869594968885</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.340833119445856</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8394796412778343</v>
+        <v>0.7189870073234553</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.7189871029765887</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8394796173645509</v>
+        <v>0.718986983410172</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.260392056209815</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8394796253356454</v>
+        <v>0.7189869913812664</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_4_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_4_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.260392056209815</v>
+        <v>0.3304369359666428</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.740833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.340833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.4985545528295873</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.260392056209815</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.340833119445856</v>
+        <v>0.8734340988987196</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.340833119445856</v>
+        <v>1.559428424762873</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.340833119445856</v>
+        <v>1.559428424762873</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.340833119445856</v>
+        <v>0.8734340988987196</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.740833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.740833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.340833119445856</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.4985545528295873</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.260392056209815</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.340833119445856</v>
+        <v>0.8734340988987196</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.340833119445856</v>
+        <v>1.559428424762873</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.340833119445856</v>
+        <v>1.559428424762873</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.340833119445856</v>
+        <v>1.559428424762873</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.340833119445856</v>
+        <v>1.559428424762873</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.340833119445856</v>
+        <v>1.559428424762873</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002911884595637675</v>
+        <v>-0.0002273669071565382</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.125377296347919</v>
+        <v>0.09789748179539395</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.340833119445856</v>
+        <v>1.559428424762873</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.251089191551114</v>
+        <v>0.1960564410573176</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.484397974606741</v>
+        <v>0.3782305729554164</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.340833119445856</v>
+        <v>0.8734340988987196</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.094830122634362</v>
+        <v>0.8548702404949264</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1490040413962465</v>
+        <v>0.1163458444926515</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.260392056209815</v>
+        <v>0.6734340988987195</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.9078253670111168</v>
+        <v>0.708852548536697</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.030234028388017</v>
+        <v>0.02360743730342368</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.740833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8190562797880638</v>
+        <v>0.6395395666804337</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02618365448335649</v>
+        <v>0.02044473209925879</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.260392056209815</v>
+        <v>0.6734340988987195</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8411568527291149</v>
+        <v>0.6567962117234636</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01280094425877406</v>
+        <v>0.009995315352035754</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.740833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.840540595716174</v>
+        <v>0.6563150219723228</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006107433898408667</v>
+        <v>0.004767749818138731</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.260392056209815</v>
+        <v>0.6734340988987195</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8399394289787253</v>
+        <v>0.6558445192388734</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002541392468708027</v>
+        <v>0.001983012135058234</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.740833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.838907762413118</v>
+        <v>0.6550378715032394</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001759812697689741</v>
+        <v>0.001373205281186654</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.260392056209815</v>
+        <v>0.6734340988987195</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8398836897104224</v>
+        <v>0.6557989126720131</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000731420068048378</v>
+        <v>0.0005703483121322848</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.340833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8395854436514759</v>
+        <v>0.6555649058131841</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003771941615533185</v>
+        <v>0.0002930045385538113</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8396069994625589</v>
+        <v>0.6555806358309134</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001451111287247665</v>
+        <v>0.0001120446912784018</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8395195778236685</v>
+        <v>0.6555112265278823</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.68865563710321e-05</v>
+        <v>5.913492526961955e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8395280723895645</v>
+        <v>0.6555167956983743</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.509169298536786e-05</v>
+        <v>2.662161700254366e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8395218419288641</v>
+        <v>0.6555108314812205</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.41817221615223e-05</v>
+        <v>9.919117236739567e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.839514501695981</v>
+        <v>0.6555040113000891</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.301093358848441e-06</v>
+        <v>1.456405945771008e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8395068983321173</v>
+        <v>0.6554969864615283</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-2.106181251314092e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8395010276058132</v>
+        <v>0.6554913092299586</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.839495162809812</v>
+        <v>0.6554856367196743</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.260392056209815</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8394894836331038</v>
+        <v>0.6554800930515718</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.340833119445856</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8394846023348544</v>
+        <v>0.6554751718978504</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.8734340988987196</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8394796811333066</v>
+        <v>0.6554752117533228</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.340833119445856</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8394796731622122</v>
+        <v>0.6554752037822282</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.8734340988987196</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8394798325841012</v>
+        <v>0.6554753632041174</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.340833119445856</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.655475267550984</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8394800876591241</v>
+        <v>0.6554756182791402</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8394798405551956</v>
+        <v>0.6554753711752118</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8394798006997234</v>
+        <v>0.6554753313197396</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.740833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.655475267550984</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8394798086708178</v>
+        <v>0.655475339290834</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.655475267550984</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.740833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8394798405551956</v>
+        <v>0.6554753711752118</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8394799362083294</v>
+        <v>0.6554754668283456</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8394798724395736</v>
+        <v>0.6554754030595896</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8394798325841012</v>
+        <v>0.6554753632041174</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8394798086708178</v>
+        <v>0.655475339290834</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8394795615668897</v>
+        <v>0.6554750921869059</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.839479481855945</v>
+        <v>0.6554750124759611</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.340833119445856</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8394795296825117</v>
+        <v>0.6554750603025279</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8394796492489288</v>
+        <v>0.6554751798689449</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.4985545528295873</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8394796333067398</v>
+        <v>0.655475163926756</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.260392056209815</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8394796492489288</v>
+        <v>0.6554751798689449</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.340833119445856</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8394796333067398</v>
+        <v>0.655475163926756</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8394796891044011</v>
+        <v>0.6554752197244172</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8394796891044011</v>
+        <v>0.6554752197244172</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.340833119445856</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8394796891044011</v>
+        <v>0.6554752197244172</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.8734340988987196</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8394798405551956</v>
+        <v>0.6554753711752118</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.340833119445856</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8394800557747463</v>
+        <v>0.6554755863947623</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.8734340988987196</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8394799680927072</v>
+        <v>0.6554754987127234</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.340833119445856</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8394799202661405</v>
+        <v>0.6554754508861567</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.260392056209815</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8394799680927072</v>
+        <v>0.6554754987127234</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8394797847575345</v>
+        <v>0.6554753153775507</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8394797927286289</v>
+        <v>0.6554753233486451</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.740833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8394798006997234</v>
+        <v>0.6554753313197396</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8394798086708178</v>
+        <v>0.655475339290834</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8394798086708178</v>
+        <v>0.655475339290834</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.740833119445856</v>
+        <v>0.8734340988987196</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8394798485262902</v>
+        <v>0.6554753791463063</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.340833119445856</v>
+        <v>1.559428424762873</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.839479912295046</v>
+        <v>0.6554754429150622</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.340833119445856</v>
+        <v>0.8734340988987197</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8394800238903684</v>
+        <v>0.6554755545103845</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8394800717169352</v>
+        <v>0.6554756023369513</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.260392056209815</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8394800318614629</v>
+        <v>0.655475562481479</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.740833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8394799601216127</v>
+        <v>0.6554754907416289</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8394800796880296</v>
+        <v>0.6554756103080458</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8394799202661405</v>
+        <v>0.6554754508861567</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8394796891044011</v>
+        <v>0.6554752197244172</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8394796412778343</v>
+        <v>0.6554751718978504</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8394796731622122</v>
+        <v>0.6554752037822282</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.655475267550984</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.655475267550984</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8394796572200233</v>
+        <v>0.6554751878400393</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.260392056209815</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8394795376536062</v>
+        <v>0.6554750682736223</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.340833119445856</v>
+        <v>0.8734340988987196</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8394794977981339</v>
+        <v>0.6554750284181501</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.340833119445856</v>
+        <v>0.8734340988987196</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8394796412778343</v>
+        <v>0.6554751718978504</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.83947977678644</v>
+        <v>0.6554753074064562</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.4985545528295873</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8394797608442511</v>
+        <v>0.6554752914642673</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.655475267550984</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8394796970754955</v>
+        <v>0.6554752276955117</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8394795934512675</v>
+        <v>0.6554751240712837</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.340833119445856</v>
+        <v>-0.01256022696543391</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8394794738848506</v>
+        <v>0.6554750045048666</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.8734340988987196</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8394795934512675</v>
+        <v>0.6554751240712837</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.340833119445856</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8394796412778343</v>
+        <v>0.6554751718978504</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6603920562098147</v>
+        <v>0.1874397730345661</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8394797369309678</v>
+        <v>0.655475267550984</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6603920562098147</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8394796173645509</v>
+        <v>0.6554751479845671</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.260392056209815</v>
+        <v>-0.6985545528295873</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8394796253356454</v>
+        <v>0.6554751559556615</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_4_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_4_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.450247198343277</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.3304369359666428</v>
+        <v>0.1199999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5555984973907471</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.1600000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4622305035591125</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.3966431617736816</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4288022220134735</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.3995989561080933</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4456935226917267</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4618687927722931</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.5424866080284119</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4265572428703308</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.1874397730345661</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4034413695335388</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4985545528295873</v>
+        <v>0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4301106631755829</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.563361644744873</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8734340988987196</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.545778214931488</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.559428424762873</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.6061149835586548</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.559428424762873</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.5253663659095764</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.8734340988987196</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4615417420864105</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4870619773864746</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.01256022696543391</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.5225903391838074</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4338224530220032</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3796514272689819</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3486240208148956</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.2963030934333801</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5055757761001587</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4231521487236023</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.1874397730345661</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4062934219837189</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4118421971797943</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6985545528295873</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4711058139801025</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6985545528295873</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4876658916473389</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6985545528295873</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.2948322594165802</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6985545528295873</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4852877259254456</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6985545528295873</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.2431353777647018</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.01256022696543391</v>
+        <v>0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.5314050912857056</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4113115072250366</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4833234250545502</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4985545528295873</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4720761477947235</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5522609353065491</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8734340988987196</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.6368867754936218</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.559428424762873</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.7705803513526917</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.559428424762873</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.644065797328949</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.559428424762873</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.9486927390098572</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.559428424762873</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.7838584184646606</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.559428424762873</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002273669071565382</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09789748179539395</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9793493151664734</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.559428424762873</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1960564410573176</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3782305729554164</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.8877878785133362</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.8734340988987196</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8548702404949264</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1163458444926515</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.01840141043066978</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.6734340988987195</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.708852548536697</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02360743730342368</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.8967235088348389</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6395395666804337</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02044473209925879</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.2455794811248779</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.6734340988987195</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6567962117234636</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009995315352035754</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.7073318958282471</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6563150219723228</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004767749818138731</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4400449097156525</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6734340988987195</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6558445192388734</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001983012135058234</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.6875324845314026</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6550378715032394</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001373205281186654</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.3736529350280762</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.6734340988987195</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6557989126720131</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005703483121322848</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.6374929547309875</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6555649058131841</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002930045385538113</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.322353720664978</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6555806358309134</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001120446912784018</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4669875800609589</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6555112265278823</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.913492526961955e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4861485660076141</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6555167956983743</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.662161700254366e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.2648312449455261</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6555108314812205</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.919117236739567e-06</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3379042446613312</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6555040113000891</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.317479133605957</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6554969864615283</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.3335947692394257</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6554913092299586</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.2775437831878662</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6554856367196743</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4873671233654022</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.1874397730345661</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6554800930515718</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.5582188963890076</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6554751718978504</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4057652354240417</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8734340988987196</v>
+        <v>0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6554752117533228</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.6987634897232056</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6554752037822282</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.3554910123348236</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8734340988987196</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6554753632041174</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.8494876623153687</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.655475267550984</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3271713256835938</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.1874397730345661</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6554756182791402</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3454648852348328</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6554753711752118</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4896982908248901</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6554753313197396</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.5029977560043335</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.655475267550984</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3528673946857452</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.655475339290834</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.341331273317337</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.655475267550984</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.8492055535316467</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.01256022696543391</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6554753711752118</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4915778040885925</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.01256022696543391</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6554754668283456</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3673790991306305</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6985545528295873</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6554754030595896</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2932405769824982</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6554753632041174</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.2063468098640442</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.655475339290834</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.304081529378891</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6554750921869059</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4595293998718262</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6554750124759611</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.5069471597671509</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6554750603025279</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.2754664123058319</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6554751798689449</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4352235794067383</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4985545528295873</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.655475163926756</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.3613068759441376</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6554751798689449</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.5273267030715942</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.655475163926756</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3700008392333984</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6554752197244172</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3090208768844604</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6554752197244172</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.7426993846893311</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1874397730345661</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6554752197244172</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.403842031955719</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.8734340988987196</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6554753711752118</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.6030627489089966</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6554755863947623</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3117100894451141</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8734340988987196</v>
+        <v>0.16</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6554754987127234</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5266333222389221</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6554754508861567</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.1822973191738129</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.1874397730345661</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6554754987127234</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3652060329914093</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6554753153775507</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3047777712345123</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6554753233486451</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.532861053943634</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6554753313197396</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2735628187656403</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.655475339290834</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3802163302898407</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.01256022696543391</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.655475339290834</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.642340362071991</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8734340988987196</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6554753791463063</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.5892450213432312</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.559428424762873</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6554754429150622</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.5358752012252808</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.8734340988987197</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6554755545103845</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.2981910407543182</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6554756023369513</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3521613776683807</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.655475562481479</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.5869247317314148</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6554754907416289</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.2221516519784927</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6554756103080458</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.2372379302978516</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6554754508861567</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3545319736003876</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6554752197244172</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4419696033000946</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6554751718978504</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4143833220005035</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6554752037822282</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3931272625923157</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.655475267550984</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.2078684121370316</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.655475267550984</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.2297953069210052</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6554751878400393</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2380920648574829</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.1874397730345661</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6554750682736223</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.5948219299316406</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.8734340988987196</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6554750284181501</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.5391945838928223</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8734340988987196</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6554751718978504</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4213135838508606</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6554753074064562</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2013542056083679</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4985545528295873</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6554752914642673</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.2833009958267212</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.655475267550984</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.2330475449562073</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6554752276955117</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.2010330110788345</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6554751240712837</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.7337961792945862</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.01256022696543391</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6554750045048666</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3730037808418274</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.8734340988987196</v>
+        <v>0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6554751240712837</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.5669575929641724</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6554751718978504</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.2156457006931305</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.1874397730345661</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.655475267550984</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3676121532917023</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6985545528295873</v>
+        <v>0.01999999999999985</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6554751479845671</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4930345416069031</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6985545528295873</v>
+        <v>-0.7200000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6554751559556615</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_4_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_4_000001.xlsx
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.5555984973907471</v>
+        <v>0.5555984377861023</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.1600000000000002</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.4618687927722931</v>
+        <v>0.4618687331676483</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.4265572428703308</v>
+        <v>0.426557183265686</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.5799999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.5253663659095764</v>
+        <v>0.5253663063049316</v>
       </c>
       <c r="JB17" t="n">
         <v>0.5799999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.2963030934333801</v>
+        <v>0.2963030636310577</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.8599999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.4231521487236023</v>
+        <v>0.4231521189212799</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.8599999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.2948322594165802</v>
+        <v>0.2948321998119354</v>
       </c>
       <c r="JB31" t="n">
         <v>0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.4852877259254456</v>
+        <v>0.4852876663208008</v>
       </c>
       <c r="JB32" t="n">
         <v>0.3</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.01840141043066978</v>
+        <v>0.01840141415596008</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.3</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.7073318958282471</v>
+        <v>0.7073319554328918</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.4399999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.2648312449455261</v>
+        <v>0.2648312151432037</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.3379042446613312</v>
+        <v>0.3379042744636536</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.3554910123348236</v>
+        <v>0.3554909825325012</v>
       </c>
       <c r="JB66" t="n">
         <v>0.16</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.3528673946857452</v>
+        <v>0.3528674244880676</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.3673790991306305</v>
+        <v>0.3673791289329529</v>
       </c>
       <c r="JB76" t="n">
         <v>0.16</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.2932405769824982</v>
+        <v>0.2932405471801758</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.1199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.304081529378891</v>
+        <v>0.3040815591812134</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.5799999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.4595293998718262</v>
+        <v>0.4595293402671814</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.3700008392333984</v>
+        <v>0.370000809431076</v>
       </c>
       <c r="JB86" t="n">
         <v>0.16</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3090208768844604</v>
+        <v>0.3090208470821381</v>
       </c>
       <c r="JB87" t="n">
         <v>0.16</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.3117100894451141</v>
+        <v>0.3117100596427917</v>
       </c>
       <c r="JB91" t="n">
         <v>0.16</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.5266333222389221</v>
+        <v>0.5266332626342773</v>
       </c>
       <c r="JB92" t="n">
         <v>0.1600000000000001</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.1822973191738129</v>
+        <v>0.1822972893714905</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.7199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.3652060329914093</v>
+        <v>0.3652060031890869</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.3802163302898407</v>
+        <v>0.3802162706851959</v>
       </c>
       <c r="JB98" t="n">
         <v>0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.5358752012252808</v>
+        <v>0.5358752608299255</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.3521613776683807</v>
+        <v>0.3521614372730255</v>
       </c>
       <c r="JB103" t="n">
         <v>0.02000000000000007</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.5869247317314148</v>
+        <v>0.5869247913360596</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.8599999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.2221516519784927</v>
+        <v>0.2221516221761703</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.8599999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.4143833220005035</v>
+        <v>0.4143832921981812</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.5799999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3931272625923157</v>
+        <v>0.3931272327899933</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.5799999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.2078684121370316</v>
+        <v>0.2078683972358704</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.8599999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.2156457006931305</v>
+        <v>0.2156457155942917</v>
       </c>
       <c r="JB124" t="n">
         <v>0.16</v>
